--- a/models/5726_DCF_Model_20260906.xlsx
+++ b/models/5726_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CDC26E7-FA33-4340-A471-7BB547A15697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47105FA-6C58-49F9-9675-2480005E5B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -876,7 +876,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-06 18:19, template rev a0efed8</t>
+    <t>Generated by pipeline on 2026-09-06 21:09, template rev b29b23d</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -1146,7 +1146,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-06 18:19:47</t>
+    <t>2026-09-06 21:09:42</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1218,7 +1218,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>a0efed8</t>
+    <t>b29b23d</t>
   </si>
   <si>
     <t>ticker</t>

--- a/models/5726_DCF_Model_20260906.xlsx
+++ b/models/5726_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47105FA-6C58-49F9-9675-2480005E5B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E5E99C-A2EB-4996-955A-1ED98447BB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="400">
   <si>
     <t>DISCLAIMER: This is a sample analysis for demonstration purposes only. It does not constitute investment advice.</t>
   </si>
@@ -876,7 +876,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-06 21:09, template rev b29b23d</t>
+    <t>Generated by pipeline on 2026-09-06 22:51, template rev 034a4bb</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -936,6 +936,12 @@
     <t>value</t>
   </si>
   <si>
+    <t>annual_doc_ids</t>
+  </si>
+  <si>
+    <t>2026-03-31=S100YHFZ, 2025-03-31=S100W7ZO, 2024-03-31=S100TSNG, 2023-03-31=S100R2LJ, 2022-03-31=S100OD4X</t>
+  </si>
+  <si>
     <t>auto_log_entries</t>
   </si>
   <si>
@@ -1119,6 +1125,12 @@
     <t>0.057487</t>
   </si>
   <si>
+    <t>disclosure_basis_date</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
     <t>fs_year_coverage</t>
   </si>
   <si>
@@ -1146,7 +1158,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-06 21:09:42</t>
+    <t>2026-09-06 22:51:15</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1218,7 +1230,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>b29b23d</t>
+    <t>034a4bb</t>
   </si>
   <si>
     <t>ticker</t>
@@ -6906,7 +6918,7 @@
   <sheetPr>
     <tabColor rgb="FF808080"/>
   </sheetPr>
-  <dimension ref="B2:G66"/>
+  <dimension ref="B2:G68"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -7064,15 +7076,15 @@
         <v>306</v>
       </c>
       <c r="C17" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C18" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -7112,23 +7124,23 @@
         <v>317</v>
       </c>
       <c r="C23" t="s">
-        <v>4</v>
+        <v>318</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C24" t="s">
-        <v>278</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C25" t="s">
-        <v>320</v>
+        <v>278</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -7136,23 +7148,23 @@
         <v>321</v>
       </c>
       <c r="C26" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C27" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C28" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -7192,31 +7204,31 @@
         <v>333</v>
       </c>
       <c r="C33" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C34" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C35" t="s">
-        <v>222</v>
+        <v>310</v>
       </c>
     </row>
     <row r="36" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C36" t="s">
-        <v>337</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -7296,15 +7308,15 @@
         <v>356</v>
       </c>
       <c r="C46" t="s">
-        <v>312</v>
+        <v>357</v>
       </c>
     </row>
     <row r="47" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C47" t="s">
-        <v>358</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -7456,6 +7468,22 @@
         <v>395</v>
       </c>
       <c r="C66" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B67" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C67" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B68" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C68" t="s">
         <v>221</v>
       </c>
     </row>

--- a/models/5726_DCF_Model_20260906.xlsx
+++ b/models/5726_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E5E99C-A2EB-4996-955A-1ED98447BB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D089F8-9DCF-4F1B-B49F-528A3F8D26BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -876,7 +876,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-06 22:51, template rev 034a4bb</t>
+    <t>Generated by pipeline on 2026-09-06 23:01, template rev 64d59e6</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -1158,7 +1158,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-06 22:51:15</t>
+    <t>2026-09-06 23:01:39</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1230,7 +1230,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>034a4bb</t>
+    <t>64d59e6</t>
   </si>
   <si>
     <t>ticker</t>

--- a/models/5726_DCF_Model_20260906.xlsx
+++ b/models/5726_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D089F8-9DCF-4F1B-B49F-528A3F8D26BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6AC072F-DA3F-4ECA-9A20-511BCF6FE660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -647,7 +647,7 @@
     <t>Comparable Company Analysis</t>
   </si>
   <si>
-    <t>Peer prices as of 2026-09-06 (Mkt Cap / EV of peer rows are static CSV values; the subject row is live-linked to Executive Summary)</t>
+    <t>Peer prices as of 2026-09-07 (Mkt Cap / EV of peer rows are static CSV values; the subject row is live-linked to Executive Summary)</t>
   </si>
   <si>
     <t>Mkt Cap
@@ -870,13 +870,13 @@
     <t>状態</t>
   </si>
   <si>
-    <t>2026-09-06</t>
+    <t>2026-09-07</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-06 23:01, template rev 64d59e6</t>
+    <t>Generated by pipeline on 2026-09-07 02:27, template rev 15b64f7</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -1158,7 +1158,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-06 23:01:39</t>
+    <t>2026-09-07 02:27:27</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1230,7 +1230,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>64d59e6</t>
+    <t>15b64f7</t>
   </si>
   <si>
     <t>ticker</t>

--- a/models/5726_DCF_Model_20260906.xlsx
+++ b/models/5726_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6AC072F-DA3F-4ECA-9A20-511BCF6FE660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8D514F-6227-418D-BC2A-CAC312CDEC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -876,7 +876,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-07 02:27, template rev 15b64f7</t>
+    <t>Generated by pipeline on 2026-09-07 12:10, template rev 42941f3</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -1158,7 +1158,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-07 02:27:27</t>
+    <t>2026-09-07 12:10:02</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1230,7 +1230,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>15b64f7</t>
+    <t>42941f3</t>
   </si>
   <si>
     <t>ticker</t>
